--- a/backend/data/financials_by_company/0W7.F.xlsx
+++ b/backend/data/financials_by_company/0W7.F.xlsx
@@ -687,127 +687,125 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-2471389.414213</v>
+        <v>136352.505537</v>
       </c>
       <c r="C2" t="n">
-        <v>0.388522</v>
+        <v>0.307793</v>
       </c>
       <c r="D2" t="n">
-        <v>57502000</v>
+        <v>43731000</v>
       </c>
       <c r="E2" t="n">
-        <v>-6361000</v>
+        <v>443000</v>
       </c>
       <c r="F2" t="n">
-        <v>-6361000</v>
+        <v>443000</v>
       </c>
       <c r="G2" t="n">
-        <v>10282000</v>
+        <v>10001000</v>
       </c>
       <c r="H2" t="n">
-        <v>27399000</v>
+        <v>22882000</v>
       </c>
       <c r="I2" t="n">
-        <v>233310000</v>
+        <v>136326000</v>
       </c>
       <c r="J2" t="n">
-        <v>51141000</v>
+        <v>44174000</v>
       </c>
       <c r="K2" t="n">
-        <v>23742000</v>
+        <v>21292000</v>
       </c>
       <c r="L2" t="n">
-        <v>-12678000</v>
+        <v>-10950000</v>
       </c>
       <c r="M2" t="n">
-        <v>6927000</v>
+        <v>6844000</v>
       </c>
       <c r="N2" t="n">
-        <v>130000</v>
+        <v>102000</v>
       </c>
       <c r="O2" t="n">
-        <v>14171610.585787</v>
+        <v>9694352.505537</v>
       </c>
       <c r="P2" t="n">
-        <v>10282000</v>
+        <v>10001000</v>
       </c>
       <c r="Q2" t="n">
-        <v>190407407</v>
+        <v>187196887</v>
       </c>
       <c r="R2" t="n">
-        <v>187618665</v>
+        <v>187196887</v>
       </c>
       <c r="S2" t="n">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
       <c r="T2" t="n">
-        <v>0.055</v>
+        <v>0.053</v>
       </c>
       <c r="U2" t="n">
-        <v>10282000</v>
+        <v>10001000</v>
       </c>
       <c r="V2" t="n">
-        <v>10282000</v>
+        <v>10001000</v>
       </c>
       <c r="W2" t="n">
-        <v>10282000</v>
+        <v>10001000</v>
       </c>
       <c r="X2" t="n">
-        <v>10282000</v>
+        <v>10001000</v>
       </c>
       <c r="Y2" t="n">
-        <v>6533000</v>
+        <v>4447000</v>
       </c>
       <c r="Z2" t="n">
-        <v>16815000</v>
+        <v>14448000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-6972000</v>
+        <v>3579000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-611000</v>
+        <v>3136000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-6361000</v>
+        <v>443000</v>
       </c>
       <c r="AD2" t="n">
-        <v>2404000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>8765000</v>
-      </c>
+        <v>443000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>-12678000</v>
+        <v>-10950000</v>
       </c>
       <c r="AG2" t="n">
-        <v>5881000</v>
+        <v>4208000</v>
       </c>
       <c r="AH2" t="n">
-        <v>6927000</v>
+        <v>6844000</v>
       </c>
       <c r="AI2" t="n">
-        <v>130000</v>
+        <v>102000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36465000</v>
+        <v>21819000</v>
       </c>
       <c r="AK2" t="n">
-        <v>211869000</v>
+        <v>162505000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1580000</v>
+        <v>72862000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-371000</v>
+        <v>270000</v>
       </c>
       <c r="AN2" t="n">
-        <v>27399000</v>
+        <v>22882000</v>
       </c>
       <c r="AO2" t="n">
-        <v>27399000</v>
+        <v>22882000</v>
       </c>
       <c r="AP2" t="n">
         <v>119000</v>
@@ -816,153 +814,157 @@
         <v>119000</v>
       </c>
       <c r="AR2" t="n">
-        <v>27280000</v>
+        <v>22763000</v>
       </c>
       <c r="AS2" t="n">
-        <v>183261000</v>
+        <v>66491000</v>
       </c>
       <c r="AT2" t="n">
-        <v>51292000</v>
+        <v>1619000</v>
       </c>
       <c r="AU2" t="n">
-        <v>131969000</v>
+        <v>64872000</v>
       </c>
       <c r="AV2" t="n">
-        <v>9728000</v>
+        <v>6367000</v>
       </c>
       <c r="AW2" t="n">
-        <v>122241000</v>
+        <v>58505000</v>
       </c>
       <c r="AX2" t="n">
-        <v>248334000</v>
+        <v>184324000</v>
       </c>
       <c r="AY2" t="n">
-        <v>233310000</v>
+        <v>136326000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>481644000</v>
+        <v>320650000</v>
       </c>
       <c r="BA2" t="n">
-        <v>481644000</v>
+        <v>320650000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>273900</v>
+        <v>64346.462715</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3</v>
+        <v>0.270363</v>
       </c>
       <c r="D3" t="n">
-        <v>38766000</v>
+        <v>40769000</v>
       </c>
       <c r="E3" t="n">
-        <v>913000</v>
+        <v>238000</v>
       </c>
       <c r="F3" t="n">
-        <v>913000</v>
+        <v>238000</v>
       </c>
       <c r="G3" t="n">
-        <v>3123000</v>
+        <v>7632000</v>
       </c>
       <c r="H3" t="n">
-        <v>28267000</v>
+        <v>24414000</v>
       </c>
       <c r="I3" t="n">
-        <v>227889000</v>
+        <v>153734000</v>
       </c>
       <c r="J3" t="n">
-        <v>39679000</v>
+        <v>41007000</v>
       </c>
       <c r="K3" t="n">
-        <v>11412000</v>
+        <v>16593000</v>
       </c>
       <c r="L3" t="n">
-        <v>-11472000</v>
+        <v>-10505000</v>
       </c>
       <c r="M3" t="n">
-        <v>5881000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>6133000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>36000</v>
+      </c>
       <c r="O3" t="n">
-        <v>2483900</v>
+        <v>7458346.462715</v>
       </c>
       <c r="P3" t="n">
-        <v>3123000</v>
+        <v>7632000</v>
       </c>
       <c r="Q3" t="n">
-        <v>195187500</v>
+        <v>190800000</v>
       </c>
       <c r="R3" t="n">
-        <v>187618665</v>
+        <v>187417598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.016</v>
+        <v>0.04</v>
       </c>
       <c r="T3" t="n">
-        <v>0.017</v>
+        <v>0.041</v>
       </c>
       <c r="U3" t="n">
-        <v>3123000</v>
+        <v>7632000</v>
       </c>
       <c r="V3" t="n">
-        <v>3123000</v>
+        <v>7632000</v>
       </c>
       <c r="W3" t="n">
-        <v>3123000</v>
+        <v>7632000</v>
       </c>
       <c r="X3" t="n">
-        <v>3123000</v>
+        <v>7632000</v>
       </c>
       <c r="Y3" t="n">
-        <v>2408000</v>
+        <v>2828000</v>
       </c>
       <c r="Z3" t="n">
-        <v>5531000</v>
+        <v>10460000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1130000</v>
+        <v>5115000</v>
       </c>
       <c r="AB3" t="n">
-        <v>217000</v>
+        <v>4877000</v>
       </c>
       <c r="AC3" t="n">
-        <v>913000</v>
+        <v>238000</v>
       </c>
       <c r="AD3" t="n">
-        <v>913000</v>
+        <v>238000</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>-11472000</v>
+        <v>-10505000</v>
       </c>
       <c r="AG3" t="n">
-        <v>5591000</v>
+        <v>4408000</v>
       </c>
       <c r="AH3" t="n">
-        <v>5881000</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
+        <v>6133000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>36000</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>15875000</v>
+        <v>15850000</v>
       </c>
       <c r="AK3" t="n">
-        <v>231688000</v>
+        <v>167267000</v>
       </c>
       <c r="AL3" t="n">
-        <v>91151000</v>
+        <v>63618000</v>
       </c>
       <c r="AM3" t="n">
-        <v>153000</v>
+        <v>512000</v>
       </c>
       <c r="AN3" t="n">
-        <v>28267000</v>
+        <v>24414000</v>
       </c>
       <c r="AO3" t="n">
-        <v>28267000</v>
+        <v>24414000</v>
       </c>
       <c r="AP3" t="n">
         <v>119000</v>
@@ -971,157 +973,153 @@
         <v>119000</v>
       </c>
       <c r="AR3" t="n">
-        <v>28148000</v>
+        <v>24295000</v>
       </c>
       <c r="AS3" t="n">
-        <v>112117000</v>
+        <v>78723000</v>
       </c>
       <c r="AT3" t="n">
-        <v>3343000</v>
+        <v>3278000</v>
       </c>
       <c r="AU3" t="n">
-        <v>108774000</v>
+        <v>75445000</v>
       </c>
       <c r="AV3" t="n">
-        <v>12250000</v>
+        <v>7120000</v>
       </c>
       <c r="AW3" t="n">
-        <v>96524000</v>
+        <v>68325000</v>
       </c>
       <c r="AX3" t="n">
-        <v>247563000</v>
+        <v>183117000</v>
       </c>
       <c r="AY3" t="n">
-        <v>227889000</v>
+        <v>153734000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>475452000</v>
+        <v>336851000</v>
       </c>
       <c r="BA3" t="n">
-        <v>475452000</v>
+        <v>336851000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>64346.462715</v>
+        <v>273900</v>
       </c>
       <c r="C4" t="n">
-        <v>0.270363</v>
+        <v>0.3</v>
       </c>
       <c r="D4" t="n">
-        <v>40769000</v>
+        <v>38766000</v>
       </c>
       <c r="E4" t="n">
-        <v>238000</v>
+        <v>913000</v>
       </c>
       <c r="F4" t="n">
-        <v>238000</v>
+        <v>913000</v>
       </c>
       <c r="G4" t="n">
-        <v>7632000</v>
+        <v>3123000</v>
       </c>
       <c r="H4" t="n">
-        <v>24414000</v>
+        <v>28267000</v>
       </c>
       <c r="I4" t="n">
-        <v>153734000</v>
+        <v>227889000</v>
       </c>
       <c r="J4" t="n">
-        <v>41007000</v>
+        <v>39679000</v>
       </c>
       <c r="K4" t="n">
-        <v>16593000</v>
+        <v>11412000</v>
       </c>
       <c r="L4" t="n">
-        <v>-10505000</v>
+        <v>-11472000</v>
       </c>
       <c r="M4" t="n">
-        <v>6133000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>36000</v>
-      </c>
+        <v>5881000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>7458346.462715</v>
+        <v>2483900</v>
       </c>
       <c r="P4" t="n">
-        <v>7632000</v>
+        <v>3123000</v>
       </c>
       <c r="Q4" t="n">
-        <v>190800000</v>
+        <v>195187500</v>
       </c>
       <c r="R4" t="n">
-        <v>187417598</v>
+        <v>187618665</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04</v>
+        <v>0.016</v>
       </c>
       <c r="T4" t="n">
-        <v>0.041</v>
+        <v>0.017</v>
       </c>
       <c r="U4" t="n">
-        <v>7632000</v>
+        <v>3123000</v>
       </c>
       <c r="V4" t="n">
-        <v>7632000</v>
+        <v>3123000</v>
       </c>
       <c r="W4" t="n">
-        <v>7632000</v>
+        <v>3123000</v>
       </c>
       <c r="X4" t="n">
-        <v>7632000</v>
+        <v>3123000</v>
       </c>
       <c r="Y4" t="n">
-        <v>2828000</v>
+        <v>2408000</v>
       </c>
       <c r="Z4" t="n">
-        <v>10460000</v>
+        <v>5531000</v>
       </c>
       <c r="AA4" t="n">
-        <v>5115000</v>
+        <v>1130000</v>
       </c>
       <c r="AB4" t="n">
-        <v>4877000</v>
+        <v>217000</v>
       </c>
       <c r="AC4" t="n">
-        <v>238000</v>
+        <v>913000</v>
       </c>
       <c r="AD4" t="n">
-        <v>238000</v>
+        <v>913000</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>-10505000</v>
+        <v>-11472000</v>
       </c>
       <c r="AG4" t="n">
-        <v>4408000</v>
+        <v>5591000</v>
       </c>
       <c r="AH4" t="n">
-        <v>6133000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>36000</v>
-      </c>
+        <v>5881000</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>15850000</v>
+        <v>15875000</v>
       </c>
       <c r="AK4" t="n">
-        <v>167267000</v>
+        <v>231688000</v>
       </c>
       <c r="AL4" t="n">
-        <v>63618000</v>
+        <v>91151000</v>
       </c>
       <c r="AM4" t="n">
-        <v>512000</v>
+        <v>153000</v>
       </c>
       <c r="AN4" t="n">
-        <v>24414000</v>
+        <v>28267000</v>
       </c>
       <c r="AO4" t="n">
-        <v>24414000</v>
+        <v>28267000</v>
       </c>
       <c r="AP4" t="n">
         <v>119000</v>
@@ -1130,157 +1128,159 @@
         <v>119000</v>
       </c>
       <c r="AR4" t="n">
-        <v>24295000</v>
+        <v>28148000</v>
       </c>
       <c r="AS4" t="n">
-        <v>78723000</v>
+        <v>112117000</v>
       </c>
       <c r="AT4" t="n">
-        <v>3278000</v>
+        <v>3343000</v>
       </c>
       <c r="AU4" t="n">
-        <v>75445000</v>
+        <v>108774000</v>
       </c>
       <c r="AV4" t="n">
-        <v>7120000</v>
+        <v>12250000</v>
       </c>
       <c r="AW4" t="n">
-        <v>68325000</v>
+        <v>96524000</v>
       </c>
       <c r="AX4" t="n">
-        <v>183117000</v>
+        <v>247563000</v>
       </c>
       <c r="AY4" t="n">
-        <v>153734000</v>
+        <v>227889000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>336851000</v>
+        <v>475452000</v>
       </c>
       <c r="BA4" t="n">
-        <v>336851000</v>
+        <v>475452000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>136352.505537</v>
+        <v>-2471389.414213</v>
       </c>
       <c r="C5" t="n">
-        <v>0.307793</v>
+        <v>0.388522</v>
       </c>
       <c r="D5" t="n">
-        <v>43731000</v>
+        <v>57502000</v>
       </c>
       <c r="E5" t="n">
-        <v>443000</v>
+        <v>-6361000</v>
       </c>
       <c r="F5" t="n">
-        <v>443000</v>
+        <v>-6361000</v>
       </c>
       <c r="G5" t="n">
-        <v>10001000</v>
+        <v>10282000</v>
       </c>
       <c r="H5" t="n">
-        <v>22882000</v>
+        <v>27399000</v>
       </c>
       <c r="I5" t="n">
-        <v>136326000</v>
+        <v>233310000</v>
       </c>
       <c r="J5" t="n">
-        <v>44174000</v>
+        <v>51141000</v>
       </c>
       <c r="K5" t="n">
-        <v>21292000</v>
+        <v>23742000</v>
       </c>
       <c r="L5" t="n">
-        <v>-10950000</v>
+        <v>-12678000</v>
       </c>
       <c r="M5" t="n">
-        <v>6844000</v>
+        <v>6927000</v>
       </c>
       <c r="N5" t="n">
-        <v>102000</v>
+        <v>130000</v>
       </c>
       <c r="O5" t="n">
-        <v>9694352.505537</v>
+        <v>14171610.585787</v>
       </c>
       <c r="P5" t="n">
-        <v>10001000</v>
+        <v>10282000</v>
       </c>
       <c r="Q5" t="n">
-        <v>187196887</v>
+        <v>190407407</v>
       </c>
       <c r="R5" t="n">
-        <v>187196887</v>
+        <v>187618665</v>
       </c>
       <c r="S5" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
       <c r="T5" t="n">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
       <c r="U5" t="n">
-        <v>10001000</v>
+        <v>10282000</v>
       </c>
       <c r="V5" t="n">
-        <v>10001000</v>
+        <v>10282000</v>
       </c>
       <c r="W5" t="n">
-        <v>10001000</v>
+        <v>10282000</v>
       </c>
       <c r="X5" t="n">
-        <v>10001000</v>
+        <v>10282000</v>
       </c>
       <c r="Y5" t="n">
-        <v>4447000</v>
+        <v>6533000</v>
       </c>
       <c r="Z5" t="n">
-        <v>14448000</v>
+        <v>16815000</v>
       </c>
       <c r="AA5" t="n">
-        <v>3579000</v>
+        <v>-6972000</v>
       </c>
       <c r="AB5" t="n">
-        <v>3136000</v>
+        <v>-611000</v>
       </c>
       <c r="AC5" t="n">
-        <v>443000</v>
+        <v>-6361000</v>
       </c>
       <c r="AD5" t="n">
-        <v>443000</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
+        <v>2404000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>8765000</v>
+      </c>
       <c r="AF5" t="n">
-        <v>-10950000</v>
+        <v>-12678000</v>
       </c>
       <c r="AG5" t="n">
-        <v>4208000</v>
+        <v>5881000</v>
       </c>
       <c r="AH5" t="n">
-        <v>6844000</v>
+        <v>6927000</v>
       </c>
       <c r="AI5" t="n">
-        <v>102000</v>
+        <v>130000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21819000</v>
+        <v>36465000</v>
       </c>
       <c r="AK5" t="n">
-        <v>162505000</v>
+        <v>211869000</v>
       </c>
       <c r="AL5" t="n">
-        <v>72862000</v>
+        <v>1580000</v>
       </c>
       <c r="AM5" t="n">
-        <v>270000</v>
+        <v>-371000</v>
       </c>
       <c r="AN5" t="n">
-        <v>22882000</v>
+        <v>27399000</v>
       </c>
       <c r="AO5" t="n">
-        <v>22882000</v>
+        <v>27399000</v>
       </c>
       <c r="AP5" t="n">
         <v>119000</v>
@@ -1289,34 +1289,34 @@
         <v>119000</v>
       </c>
       <c r="AR5" t="n">
-        <v>22763000</v>
+        <v>27280000</v>
       </c>
       <c r="AS5" t="n">
-        <v>66491000</v>
+        <v>183261000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1619000</v>
+        <v>51292000</v>
       </c>
       <c r="AU5" t="n">
-        <v>64872000</v>
+        <v>131969000</v>
       </c>
       <c r="AV5" t="n">
-        <v>6367000</v>
+        <v>9728000</v>
       </c>
       <c r="AW5" t="n">
-        <v>58505000</v>
+        <v>122241000</v>
       </c>
       <c r="AX5" t="n">
-        <v>184324000</v>
+        <v>248334000</v>
       </c>
       <c r="AY5" t="n">
-        <v>136326000</v>
+        <v>233310000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>320650000</v>
+        <v>481644000</v>
       </c>
       <c r="BA5" t="n">
-        <v>320650000</v>
+        <v>481644000</v>
       </c>
     </row>
   </sheetData>
@@ -1697,137 +1697,139 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>187618665</v>
+        <v>187196887</v>
       </c>
       <c r="C2" t="n">
-        <v>187618665</v>
+        <v>187196887</v>
       </c>
       <c r="D2" t="n">
-        <v>47624000</v>
+        <v>48848000</v>
       </c>
       <c r="E2" t="n">
-        <v>202902000</v>
+        <v>171023000</v>
       </c>
       <c r="F2" t="n">
-        <v>132519000</v>
+        <v>110551000</v>
       </c>
       <c r="G2" t="n">
-        <v>200849000</v>
+        <v>184041000</v>
       </c>
       <c r="H2" t="n">
-        <v>39678000</v>
+        <v>24864000</v>
       </c>
       <c r="I2" t="n">
-        <v>132519000</v>
+        <v>110551000</v>
       </c>
       <c r="J2" t="n">
-        <v>136617000</v>
+        <v>99935000</v>
       </c>
       <c r="K2" t="n">
-        <v>134564000</v>
+        <v>112953000</v>
       </c>
       <c r="L2" t="n">
-        <v>193776000</v>
+        <v>175591000</v>
       </c>
       <c r="M2" t="n">
-        <v>134564000</v>
+        <v>112953000</v>
       </c>
       <c r="N2" t="n">
-        <v>134564000</v>
+        <v>112953000</v>
       </c>
       <c r="O2" t="n">
-        <v>-354340000</v>
+        <v>-354227000</v>
       </c>
       <c r="P2" t="n">
-        <v>-353505000</v>
+        <v>-353967000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-835000</v>
+        <v>-260000</v>
       </c>
       <c r="R2" t="n">
-        <v>77340000</v>
+        <v>56265000</v>
       </c>
       <c r="S2" t="n">
-        <v>411564000</v>
+        <v>410915000</v>
       </c>
       <c r="T2" t="n">
-        <v>411564000</v>
+        <v>410915000</v>
       </c>
       <c r="U2" t="n">
-        <v>278547000</v>
+        <v>228829000</v>
       </c>
       <c r="V2" t="n">
-        <v>188220000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>156512000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>46000</v>
+      </c>
       <c r="X2" t="n">
-        <v>2461000</v>
+        <v>559000</v>
       </c>
       <c r="Y2" t="n">
-        <v>2461000</v>
+        <v>559000</v>
       </c>
       <c r="Z2" t="n">
-        <v>185759000</v>
+        <v>155907000</v>
       </c>
       <c r="AA2" t="n">
-        <v>126547000</v>
+        <v>93269000</v>
       </c>
       <c r="AB2" t="n">
-        <v>59212000</v>
+        <v>62638000</v>
       </c>
       <c r="AC2" t="n">
-        <v>90327000</v>
+        <v>72317000</v>
       </c>
       <c r="AD2" t="n">
-        <v>4656000</v>
+        <v>1105000</v>
       </c>
       <c r="AE2" t="n">
-        <v>4656000</v>
+        <v>1105000</v>
       </c>
       <c r="AF2" t="n">
-        <v>17143000</v>
+        <v>15116000</v>
       </c>
       <c r="AG2" t="n">
-        <v>10070000</v>
+        <v>6666000</v>
       </c>
       <c r="AH2" t="n">
-        <v>7073000</v>
+        <v>8450000</v>
       </c>
       <c r="AI2" t="n">
-        <v>7073000</v>
+        <v>8450000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>9297000</v>
+        <v>6501000</v>
       </c>
       <c r="AK2" t="n">
-        <v>4616000</v>
+        <v>6518000</v>
       </c>
       <c r="AL2" t="n">
-        <v>54615000</v>
+        <v>43077000</v>
       </c>
       <c r="AM2" t="n">
-        <v>54615000</v>
+        <v>43077000</v>
       </c>
       <c r="AN2" t="n">
-        <v>37460000</v>
+        <v>25779000</v>
       </c>
       <c r="AO2" t="n">
-        <v>17155000</v>
+        <v>17298000</v>
       </c>
       <c r="AP2" t="n">
-        <v>413111000</v>
+        <v>358291000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>283106000</v>
+        <v>261110000</v>
       </c>
       <c r="AR2" t="n">
-        <v>2572000</v>
+        <v>6945000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2572000</v>
+        <v>6945000</v>
       </c>
       <c r="AT2" t="n">
         <v>7000</v>
@@ -1836,81 +1838,81 @@
         <v>7000</v>
       </c>
       <c r="AV2" t="n">
-        <v>2045000</v>
+        <v>2402000</v>
       </c>
       <c r="AW2" t="n">
-        <v>2045000</v>
+        <v>2402000</v>
       </c>
       <c r="AX2" t="n">
-        <v>278482000</v>
+        <v>251756000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-178956000</v>
+        <v>-124908000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>457438000</v>
+        <v>376664000</v>
       </c>
       <c r="BA2" t="n">
-        <v>27477000</v>
+        <v>22231000</v>
       </c>
       <c r="BB2" t="n">
-        <v>7478000</v>
+        <v>18262000</v>
       </c>
       <c r="BC2" t="n">
-        <v>141422000</v>
+        <v>104315000</v>
       </c>
       <c r="BD2" t="n">
-        <v>281061000</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>209625000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>22231000</v>
+      </c>
       <c r="BF2" t="n">
-        <v>130005000</v>
+        <v>97181000</v>
       </c>
       <c r="BG2" t="n">
-        <v>2309000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>650000</v>
-      </c>
+        <v>618000</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="n">
-        <v>39866000</v>
+        <v>24308000</v>
       </c>
       <c r="BL2" t="n">
-        <v>19243000</v>
+        <v>11667000</v>
       </c>
       <c r="BM2" t="n">
-        <v>300000</v>
+        <v>747000</v>
       </c>
       <c r="BN2" t="n">
-        <v>20323000</v>
+        <v>11894000</v>
       </c>
       <c r="BO2" t="n">
-        <v>68519000</v>
+        <v>50015000</v>
       </c>
       <c r="BP2" t="n">
-        <v>-1481000</v>
+        <v>-759000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3994000</v>
+        <v>789000</v>
       </c>
       <c r="BR2" t="n">
-        <v>66006000</v>
+        <v>49985000</v>
       </c>
       <c r="BS2" t="n">
-        <v>18661000</v>
+        <v>22240000</v>
       </c>
       <c r="BT2" t="n">
-        <v>18661000</v>
+        <v>22240000</v>
       </c>
       <c r="BU2" t="n">
-        <v>18661000</v>
+        <v>22240000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
         <v>187618665</v>
@@ -1919,49 +1921,49 @@
         <v>187618665</v>
       </c>
       <c r="D3" t="n">
-        <v>93375000</v>
+        <v>82096000</v>
       </c>
       <c r="E3" t="n">
-        <v>248854000</v>
+        <v>204387000</v>
       </c>
       <c r="F3" t="n">
-        <v>121815000</v>
+        <v>118617000</v>
       </c>
       <c r="G3" t="n">
-        <v>228717000</v>
+        <v>215196000</v>
       </c>
       <c r="H3" t="n">
-        <v>41728000</v>
+        <v>27885000</v>
       </c>
       <c r="I3" t="n">
-        <v>121815000</v>
+        <v>118617000</v>
       </c>
       <c r="J3" t="n">
-        <v>144116000</v>
+        <v>110091000</v>
       </c>
       <c r="K3" t="n">
-        <v>123979000</v>
+        <v>120900000</v>
       </c>
       <c r="L3" t="n">
-        <v>205691000</v>
+        <v>190288000</v>
       </c>
       <c r="M3" t="n">
-        <v>123979000</v>
+        <v>120900000</v>
       </c>
       <c r="N3" t="n">
-        <v>123979000</v>
+        <v>120900000</v>
       </c>
       <c r="O3" t="n">
-        <v>-354643000</v>
+        <v>-354599000</v>
       </c>
       <c r="P3" t="n">
-        <v>-354429000</v>
+        <v>-354327000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-214000</v>
+        <v>-272000</v>
       </c>
       <c r="R3" t="n">
-        <v>67058000</v>
+        <v>63935000</v>
       </c>
       <c r="S3" t="n">
         <v>411564000</v>
@@ -1970,73 +1972,77 @@
         <v>411564000</v>
       </c>
       <c r="U3" t="n">
-        <v>326692000</v>
+        <v>273557000</v>
       </c>
       <c r="V3" t="n">
-        <v>216034000</v>
+        <v>172866000</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>610000</v>
+        <v>620000</v>
       </c>
       <c r="Y3" t="n">
-        <v>610000</v>
+        <v>620000</v>
       </c>
       <c r="Z3" t="n">
-        <v>215424000</v>
+        <v>172246000</v>
       </c>
       <c r="AA3" t="n">
-        <v>133712000</v>
+        <v>102858000</v>
       </c>
       <c r="AB3" t="n">
-        <v>81712000</v>
+        <v>69388000</v>
       </c>
       <c r="AC3" t="n">
-        <v>110658000</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+        <v>100691000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>71000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>71000</v>
+      </c>
       <c r="AF3" t="n">
-        <v>33430000</v>
+        <v>32141000</v>
       </c>
       <c r="AG3" t="n">
-        <v>10404000</v>
+        <v>7233000</v>
       </c>
       <c r="AH3" t="n">
-        <v>23026000</v>
+        <v>24908000</v>
       </c>
       <c r="AI3" t="n">
-        <v>23026000</v>
+        <v>24908000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8323000</v>
+        <v>7698000</v>
       </c>
       <c r="AK3" t="n">
-        <v>4382000</v>
+        <v>1472000</v>
       </c>
       <c r="AL3" t="n">
-        <v>64523000</v>
+        <v>59309000</v>
       </c>
       <c r="AM3" t="n">
-        <v>64523000</v>
+        <v>59309000</v>
       </c>
       <c r="AN3" t="n">
-        <v>37237000</v>
+        <v>31852000</v>
       </c>
       <c r="AO3" t="n">
-        <v>27286000</v>
+        <v>27457000</v>
       </c>
       <c r="AP3" t="n">
-        <v>450671000</v>
+        <v>394457000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>298285000</v>
+        <v>265881000</v>
       </c>
       <c r="AR3" t="n">
-        <v>2058000</v>
+        <v>4456000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2058000</v>
+        <v>4456000</v>
       </c>
       <c r="AT3" t="n">
         <v>7000</v>
@@ -2045,85 +2051,81 @@
         <v>7000</v>
       </c>
       <c r="AV3" t="n">
-        <v>2164000</v>
+        <v>2283000</v>
       </c>
       <c r="AW3" t="n">
-        <v>2164000</v>
+        <v>2283000</v>
       </c>
       <c r="AX3" t="n">
-        <v>294056000</v>
+        <v>259135000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-162906000</v>
+        <v>-136701000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>456962000</v>
+        <v>395836000</v>
       </c>
       <c r="BA3" t="n">
-        <v>27427000</v>
+        <v>22268000</v>
       </c>
       <c r="BB3" t="n">
-        <v>20200000</v>
+        <v>25472000</v>
       </c>
       <c r="BC3" t="n">
-        <v>153647000</v>
+        <v>115731000</v>
       </c>
       <c r="BD3" t="n">
-        <v>255688000</v>
+        <v>232365000</v>
       </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
-        <v>152386000</v>
+        <v>128576000</v>
       </c>
       <c r="BG3" t="n">
-        <v>1464000</v>
+        <v>1005000</v>
       </c>
       <c r="BH3" t="n">
-        <v>1257000</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>1899000</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1899000</v>
-      </c>
+        <v>42000</v>
+      </c>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>41255000</v>
+        <v>50340000</v>
       </c>
       <c r="BL3" t="n">
-        <v>16474000</v>
+        <v>21844000</v>
       </c>
       <c r="BM3" t="n">
-        <v>518000</v>
+        <v>153000</v>
       </c>
       <c r="BN3" t="n">
-        <v>24263000</v>
+        <v>28343000</v>
       </c>
       <c r="BO3" t="n">
-        <v>95148000</v>
+        <v>64989000</v>
       </c>
       <c r="BP3" t="n">
-        <v>-1314000</v>
+        <v>-1161000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>13212000</v>
+        <v>812000</v>
       </c>
       <c r="BR3" t="n">
-        <v>83250000</v>
+        <v>65338000</v>
       </c>
       <c r="BS3" t="n">
-        <v>11363000</v>
+        <v>12200000</v>
       </c>
       <c r="BT3" t="n">
-        <v>11363000</v>
+        <v>12200000</v>
       </c>
       <c r="BU3" t="n">
-        <v>11363000</v>
+        <v>12200000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>187618665</v>
@@ -2132,49 +2134,49 @@
         <v>187618665</v>
       </c>
       <c r="D4" t="n">
-        <v>82096000</v>
+        <v>93375000</v>
       </c>
       <c r="E4" t="n">
-        <v>204387000</v>
+        <v>248854000</v>
       </c>
       <c r="F4" t="n">
-        <v>118617000</v>
+        <v>121815000</v>
       </c>
       <c r="G4" t="n">
-        <v>215196000</v>
+        <v>228717000</v>
       </c>
       <c r="H4" t="n">
-        <v>27885000</v>
+        <v>41728000</v>
       </c>
       <c r="I4" t="n">
-        <v>118617000</v>
+        <v>121815000</v>
       </c>
       <c r="J4" t="n">
-        <v>110091000</v>
+        <v>144116000</v>
       </c>
       <c r="K4" t="n">
-        <v>120900000</v>
+        <v>123979000</v>
       </c>
       <c r="L4" t="n">
-        <v>190288000</v>
+        <v>205691000</v>
       </c>
       <c r="M4" t="n">
-        <v>120900000</v>
+        <v>123979000</v>
       </c>
       <c r="N4" t="n">
-        <v>120900000</v>
+        <v>123979000</v>
       </c>
       <c r="O4" t="n">
-        <v>-354599000</v>
+        <v>-354643000</v>
       </c>
       <c r="P4" t="n">
-        <v>-354327000</v>
+        <v>-354429000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-272000</v>
+        <v>-214000</v>
       </c>
       <c r="R4" t="n">
-        <v>63935000</v>
+        <v>67058000</v>
       </c>
       <c r="S4" t="n">
         <v>411564000</v>
@@ -2183,77 +2185,73 @@
         <v>411564000</v>
       </c>
       <c r="U4" t="n">
-        <v>273557000</v>
+        <v>326692000</v>
       </c>
       <c r="V4" t="n">
-        <v>172866000</v>
+        <v>216034000</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>620000</v>
+        <v>610000</v>
       </c>
       <c r="Y4" t="n">
-        <v>620000</v>
+        <v>610000</v>
       </c>
       <c r="Z4" t="n">
-        <v>172246000</v>
+        <v>215424000</v>
       </c>
       <c r="AA4" t="n">
-        <v>102858000</v>
+        <v>133712000</v>
       </c>
       <c r="AB4" t="n">
-        <v>69388000</v>
+        <v>81712000</v>
       </c>
       <c r="AC4" t="n">
-        <v>100691000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>71000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>71000</v>
-      </c>
+        <v>110658000</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>32141000</v>
+        <v>33430000</v>
       </c>
       <c r="AG4" t="n">
-        <v>7233000</v>
+        <v>10404000</v>
       </c>
       <c r="AH4" t="n">
-        <v>24908000</v>
+        <v>23026000</v>
       </c>
       <c r="AI4" t="n">
-        <v>24908000</v>
+        <v>23026000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>7698000</v>
+        <v>8323000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1472000</v>
+        <v>4382000</v>
       </c>
       <c r="AL4" t="n">
-        <v>59309000</v>
+        <v>64523000</v>
       </c>
       <c r="AM4" t="n">
-        <v>59309000</v>
+        <v>64523000</v>
       </c>
       <c r="AN4" t="n">
-        <v>31852000</v>
+        <v>37237000</v>
       </c>
       <c r="AO4" t="n">
-        <v>27457000</v>
+        <v>27286000</v>
       </c>
       <c r="AP4" t="n">
-        <v>394457000</v>
+        <v>450671000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>265881000</v>
+        <v>298285000</v>
       </c>
       <c r="AR4" t="n">
-        <v>4456000</v>
+        <v>2058000</v>
       </c>
       <c r="AS4" t="n">
-        <v>4456000</v>
+        <v>2058000</v>
       </c>
       <c r="AT4" t="n">
         <v>7000</v>
@@ -2262,213 +2260,215 @@
         <v>7000</v>
       </c>
       <c r="AV4" t="n">
-        <v>2283000</v>
+        <v>2164000</v>
       </c>
       <c r="AW4" t="n">
-        <v>2283000</v>
+        <v>2164000</v>
       </c>
       <c r="AX4" t="n">
-        <v>259135000</v>
+        <v>294056000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-136701000</v>
+        <v>-162906000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>395836000</v>
+        <v>456962000</v>
       </c>
       <c r="BA4" t="n">
-        <v>22268000</v>
+        <v>27427000</v>
       </c>
       <c r="BB4" t="n">
-        <v>25472000</v>
+        <v>20200000</v>
       </c>
       <c r="BC4" t="n">
-        <v>115731000</v>
+        <v>153647000</v>
       </c>
       <c r="BD4" t="n">
-        <v>232365000</v>
+        <v>255688000</v>
       </c>
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>128576000</v>
+        <v>152386000</v>
       </c>
       <c r="BG4" t="n">
-        <v>1005000</v>
+        <v>1464000</v>
       </c>
       <c r="BH4" t="n">
-        <v>42000</v>
-      </c>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
+        <v>1257000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1899000</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1899000</v>
+      </c>
       <c r="BK4" t="n">
-        <v>50340000</v>
+        <v>41255000</v>
       </c>
       <c r="BL4" t="n">
-        <v>21844000</v>
+        <v>16474000</v>
       </c>
       <c r="BM4" t="n">
-        <v>153000</v>
+        <v>518000</v>
       </c>
       <c r="BN4" t="n">
-        <v>28343000</v>
+        <v>24263000</v>
       </c>
       <c r="BO4" t="n">
-        <v>64989000</v>
+        <v>95148000</v>
       </c>
       <c r="BP4" t="n">
-        <v>-1161000</v>
+        <v>-1314000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>812000</v>
+        <v>13212000</v>
       </c>
       <c r="BR4" t="n">
-        <v>65338000</v>
+        <v>83250000</v>
       </c>
       <c r="BS4" t="n">
-        <v>12200000</v>
+        <v>11363000</v>
       </c>
       <c r="BT4" t="n">
-        <v>12200000</v>
+        <v>11363000</v>
       </c>
       <c r="BU4" t="n">
-        <v>12200000</v>
+        <v>11363000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>187196887</v>
+        <v>187618665</v>
       </c>
       <c r="C5" t="n">
-        <v>187196887</v>
+        <v>187618665</v>
       </c>
       <c r="D5" t="n">
-        <v>48848000</v>
+        <v>47624000</v>
       </c>
       <c r="E5" t="n">
-        <v>171023000</v>
+        <v>202902000</v>
       </c>
       <c r="F5" t="n">
-        <v>110551000</v>
+        <v>132519000</v>
       </c>
       <c r="G5" t="n">
-        <v>184041000</v>
+        <v>200849000</v>
       </c>
       <c r="H5" t="n">
-        <v>24864000</v>
+        <v>39678000</v>
       </c>
       <c r="I5" t="n">
-        <v>110551000</v>
+        <v>132519000</v>
       </c>
       <c r="J5" t="n">
-        <v>99935000</v>
+        <v>136617000</v>
       </c>
       <c r="K5" t="n">
-        <v>112953000</v>
+        <v>134564000</v>
       </c>
       <c r="L5" t="n">
-        <v>175591000</v>
+        <v>193776000</v>
       </c>
       <c r="M5" t="n">
-        <v>112953000</v>
+        <v>134564000</v>
       </c>
       <c r="N5" t="n">
-        <v>112953000</v>
+        <v>134564000</v>
       </c>
       <c r="O5" t="n">
-        <v>-354227000</v>
+        <v>-354340000</v>
       </c>
       <c r="P5" t="n">
-        <v>-353967000</v>
+        <v>-353505000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-260000</v>
+        <v>-835000</v>
       </c>
       <c r="R5" t="n">
-        <v>56265000</v>
+        <v>77340000</v>
       </c>
       <c r="S5" t="n">
-        <v>410915000</v>
+        <v>411564000</v>
       </c>
       <c r="T5" t="n">
-        <v>410915000</v>
+        <v>411564000</v>
       </c>
       <c r="U5" t="n">
-        <v>228829000</v>
+        <v>278547000</v>
       </c>
       <c r="V5" t="n">
-        <v>156512000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>46000</v>
-      </c>
+        <v>188220000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>559000</v>
+        <v>2461000</v>
       </c>
       <c r="Y5" t="n">
-        <v>559000</v>
+        <v>2461000</v>
       </c>
       <c r="Z5" t="n">
-        <v>155907000</v>
+        <v>185759000</v>
       </c>
       <c r="AA5" t="n">
-        <v>93269000</v>
+        <v>126547000</v>
       </c>
       <c r="AB5" t="n">
-        <v>62638000</v>
+        <v>59212000</v>
       </c>
       <c r="AC5" t="n">
-        <v>72317000</v>
+        <v>90327000</v>
       </c>
       <c r="AD5" t="n">
-        <v>1105000</v>
+        <v>4656000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1105000</v>
+        <v>4656000</v>
       </c>
       <c r="AF5" t="n">
-        <v>15116000</v>
+        <v>17143000</v>
       </c>
       <c r="AG5" t="n">
-        <v>6666000</v>
+        <v>10070000</v>
       </c>
       <c r="AH5" t="n">
-        <v>8450000</v>
+        <v>7073000</v>
       </c>
       <c r="AI5" t="n">
-        <v>8450000</v>
+        <v>7073000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6501000</v>
+        <v>9297000</v>
       </c>
       <c r="AK5" t="n">
-        <v>6518000</v>
+        <v>4616000</v>
       </c>
       <c r="AL5" t="n">
-        <v>43077000</v>
+        <v>54615000</v>
       </c>
       <c r="AM5" t="n">
-        <v>43077000</v>
+        <v>54615000</v>
       </c>
       <c r="AN5" t="n">
-        <v>25779000</v>
+        <v>37460000</v>
       </c>
       <c r="AO5" t="n">
-        <v>17298000</v>
+        <v>17155000</v>
       </c>
       <c r="AP5" t="n">
-        <v>358291000</v>
+        <v>413111000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>261110000</v>
+        <v>283106000</v>
       </c>
       <c r="AR5" t="n">
-        <v>6945000</v>
+        <v>2572000</v>
       </c>
       <c r="AS5" t="n">
-        <v>6945000</v>
+        <v>2572000</v>
       </c>
       <c r="AT5" t="n">
         <v>7000</v>
@@ -2477,76 +2477,76 @@
         <v>7000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2402000</v>
+        <v>2045000</v>
       </c>
       <c r="AW5" t="n">
-        <v>2402000</v>
+        <v>2045000</v>
       </c>
       <c r="AX5" t="n">
-        <v>251756000</v>
+        <v>278482000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-124908000</v>
+        <v>-178956000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>376664000</v>
+        <v>457438000</v>
       </c>
       <c r="BA5" t="n">
-        <v>22231000</v>
+        <v>27477000</v>
       </c>
       <c r="BB5" t="n">
-        <v>18262000</v>
+        <v>7478000</v>
       </c>
       <c r="BC5" t="n">
-        <v>104315000</v>
+        <v>141422000</v>
       </c>
       <c r="BD5" t="n">
-        <v>209625000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>22231000</v>
-      </c>
+        <v>281061000</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>97181000</v>
+        <v>130005000</v>
       </c>
       <c r="BG5" t="n">
-        <v>618000</v>
-      </c>
-      <c r="BH5" t="inlineStr"/>
+        <v>2309000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>650000</v>
+      </c>
       <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="inlineStr"/>
       <c r="BK5" t="n">
-        <v>24308000</v>
+        <v>39866000</v>
       </c>
       <c r="BL5" t="n">
-        <v>11667000</v>
+        <v>19243000</v>
       </c>
       <c r="BM5" t="n">
-        <v>747000</v>
+        <v>300000</v>
       </c>
       <c r="BN5" t="n">
-        <v>11894000</v>
+        <v>20323000</v>
       </c>
       <c r="BO5" t="n">
-        <v>50015000</v>
+        <v>68519000</v>
       </c>
       <c r="BP5" t="n">
-        <v>-759000</v>
+        <v>-1481000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>789000</v>
+        <v>3994000</v>
       </c>
       <c r="BR5" t="n">
-        <v>49985000</v>
+        <v>66006000</v>
       </c>
       <c r="BS5" t="n">
-        <v>22240000</v>
+        <v>18661000</v>
       </c>
       <c r="BT5" t="n">
-        <v>22240000</v>
+        <v>18661000</v>
       </c>
       <c r="BU5" t="n">
-        <v>22240000</v>
+        <v>18661000</v>
       </c>
     </row>
   </sheetData>
@@ -2747,422 +2747,422 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>48737000</v>
+        <v>37620000</v>
       </c>
       <c r="C2" t="n">
-        <v>-47629000</v>
+        <v>-19231000</v>
       </c>
       <c r="D2" t="n">
-        <v>9175000</v>
+        <v>3845000</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-23859000</v>
+        <v>-15480000</v>
       </c>
       <c r="G2" t="n">
-        <v>12585000</v>
+        <v>11139000</v>
       </c>
       <c r="H2" t="n">
-        <v>492000</v>
+        <v>582000</v>
       </c>
       <c r="I2" t="n">
-        <v>18661000</v>
+        <v>22240000</v>
       </c>
       <c r="J2" t="n">
-        <v>11363000</v>
+        <v>3436000</v>
       </c>
       <c r="K2" t="n">
-        <v>-613000</v>
+        <v>13000</v>
       </c>
       <c r="L2" t="n">
-        <v>7911000</v>
+        <v>18791000</v>
       </c>
       <c r="M2" t="n">
-        <v>-44265000</v>
+        <v>-18009000</v>
       </c>
       <c r="N2" t="n">
-        <v>-44265000</v>
+        <v>-18009000</v>
       </c>
       <c r="O2" t="n">
-        <v>-11622000</v>
+        <v>-5246000</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>-38454000</v>
+        <v>-15386000</v>
       </c>
       <c r="S2" t="n">
-        <v>-38454000</v>
+        <v>-15386000</v>
       </c>
       <c r="T2" t="n">
-        <v>-47629000</v>
+        <v>-19231000</v>
       </c>
       <c r="U2" t="n">
-        <v>9175000</v>
+        <v>3845000</v>
       </c>
       <c r="V2" t="n">
-        <v>-20420000</v>
+        <v>-16300000</v>
       </c>
       <c r="W2" t="n">
-        <v>-20420000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+        <v>-16300000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-2050000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-2050000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>-20420000</v>
+        <v>-14250000</v>
       </c>
       <c r="AA2" t="n">
-        <v>3439000</v>
+        <v>1230000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-23859000</v>
+        <v>-15480000</v>
       </c>
       <c r="AC2" t="n">
-        <v>72596000</v>
+        <v>53100000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-492000</v>
+        <v>-582000</v>
       </c>
       <c r="AE2" t="n">
-        <v>130000</v>
+        <v>102000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-12585000</v>
+        <v>-11139000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1214000</v>
+        <v>1005000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-475794000</v>
+        <v>-295962000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-475794000</v>
+        <v>-295962000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>560123000</v>
+        <v>359676000</v>
       </c>
       <c r="AK2" t="n">
-        <v>560123000</v>
+        <v>359676000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>1644000</v>
+        <v>-20104000</v>
       </c>
       <c r="C3" t="n">
-        <v>-13829000</v>
+        <v>-14555000</v>
       </c>
       <c r="D3" t="n">
-        <v>14044000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>26679000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>649000</v>
+      </c>
       <c r="F3" t="n">
-        <v>-15151000</v>
+        <v>-23975000</v>
       </c>
       <c r="G3" t="n">
-        <v>11523000</v>
+        <v>10400000</v>
       </c>
       <c r="H3" t="n">
-        <v>1980000</v>
+        <v>1373000</v>
       </c>
       <c r="I3" t="n">
-        <v>11363000</v>
+        <v>12200000</v>
       </c>
       <c r="J3" t="n">
-        <v>12200000</v>
+        <v>22240000</v>
       </c>
       <c r="K3" t="n">
-        <v>59000</v>
+        <v>19000</v>
       </c>
       <c r="L3" t="n">
-        <v>-896000</v>
+        <v>-10059000</v>
       </c>
       <c r="M3" t="n">
-        <v>-3675000</v>
+        <v>9625000</v>
       </c>
       <c r="N3" t="n">
-        <v>-3675000</v>
+        <v>9625000</v>
       </c>
       <c r="O3" t="n">
-        <v>-7780000</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+        <v>-6296000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>649000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>649000</v>
+      </c>
       <c r="R3" t="n">
-        <v>215000</v>
+        <v>12124000</v>
       </c>
       <c r="S3" t="n">
-        <v>215000</v>
+        <v>12124000</v>
       </c>
       <c r="T3" t="n">
-        <v>-13829000</v>
+        <v>-14555000</v>
       </c>
       <c r="U3" t="n">
-        <v>14044000</v>
+        <v>26679000</v>
       </c>
       <c r="V3" t="n">
-        <v>-14016000</v>
+        <v>-23555000</v>
       </c>
       <c r="W3" t="n">
-        <v>-14016000</v>
+        <v>-23555000</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>-14016000</v>
+        <v>-23555000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1135000</v>
+        <v>420000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-15151000</v>
+        <v>-23975000</v>
       </c>
       <c r="AC3" t="n">
-        <v>16795000</v>
+        <v>3871000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1980000</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
+        <v>-1373000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>36000</v>
+      </c>
       <c r="AF3" t="n">
-        <v>-11523000</v>
+        <v>-10400000</v>
       </c>
       <c r="AG3" t="n">
-        <v>691000</v>
+        <v>1104000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-460366000</v>
+        <v>-339585000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-460366000</v>
+        <v>-339585000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>489973000</v>
+        <v>354089000</v>
       </c>
       <c r="AK3" t="n">
-        <v>489973000</v>
+        <v>354089000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-20104000</v>
+        <v>1644000</v>
       </c>
       <c r="C4" t="n">
-        <v>-14555000</v>
+        <v>-13829000</v>
       </c>
       <c r="D4" t="n">
-        <v>26679000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>649000</v>
-      </c>
+        <v>14044000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-23975000</v>
+        <v>-15151000</v>
       </c>
       <c r="G4" t="n">
-        <v>10400000</v>
+        <v>11523000</v>
       </c>
       <c r="H4" t="n">
-        <v>1373000</v>
+        <v>1980000</v>
       </c>
       <c r="I4" t="n">
+        <v>11363000</v>
+      </c>
+      <c r="J4" t="n">
         <v>12200000</v>
       </c>
-      <c r="J4" t="n">
-        <v>22240000</v>
-      </c>
       <c r="K4" t="n">
-        <v>19000</v>
+        <v>59000</v>
       </c>
       <c r="L4" t="n">
-        <v>-10059000</v>
+        <v>-896000</v>
       </c>
       <c r="M4" t="n">
-        <v>9625000</v>
+        <v>-3675000</v>
       </c>
       <c r="N4" t="n">
-        <v>9625000</v>
+        <v>-3675000</v>
       </c>
       <c r="O4" t="n">
-        <v>-6296000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>649000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>649000</v>
-      </c>
+        <v>-7780000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>12124000</v>
+        <v>215000</v>
       </c>
       <c r="S4" t="n">
-        <v>12124000</v>
+        <v>215000</v>
       </c>
       <c r="T4" t="n">
-        <v>-14555000</v>
+        <v>-13829000</v>
       </c>
       <c r="U4" t="n">
-        <v>26679000</v>
+        <v>14044000</v>
       </c>
       <c r="V4" t="n">
-        <v>-23555000</v>
+        <v>-14016000</v>
       </c>
       <c r="W4" t="n">
-        <v>-23555000</v>
+        <v>-14016000</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>-23555000</v>
+        <v>-14016000</v>
       </c>
       <c r="AA4" t="n">
-        <v>420000</v>
+        <v>1135000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-23975000</v>
+        <v>-15151000</v>
       </c>
       <c r="AC4" t="n">
-        <v>3871000</v>
+        <v>16795000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1373000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>36000</v>
-      </c>
+        <v>-1980000</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>-10400000</v>
+        <v>-11523000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1104000</v>
+        <v>691000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-339585000</v>
+        <v>-460366000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-339585000</v>
+        <v>-460366000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>354089000</v>
+        <v>489973000</v>
       </c>
       <c r="AK4" t="n">
-        <v>354089000</v>
+        <v>489973000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>37620000</v>
+        <v>48737000</v>
       </c>
       <c r="C5" t="n">
-        <v>-19231000</v>
+        <v>-47629000</v>
       </c>
       <c r="D5" t="n">
-        <v>3845000</v>
+        <v>9175000</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-15480000</v>
+        <v>-23859000</v>
       </c>
       <c r="G5" t="n">
-        <v>11139000</v>
+        <v>12585000</v>
       </c>
       <c r="H5" t="n">
-        <v>582000</v>
+        <v>492000</v>
       </c>
       <c r="I5" t="n">
-        <v>22240000</v>
+        <v>18661000</v>
       </c>
       <c r="J5" t="n">
-        <v>3436000</v>
+        <v>11363000</v>
       </c>
       <c r="K5" t="n">
-        <v>13000</v>
+        <v>-613000</v>
       </c>
       <c r="L5" t="n">
-        <v>18791000</v>
+        <v>7911000</v>
       </c>
       <c r="M5" t="n">
-        <v>-18009000</v>
+        <v>-44265000</v>
       </c>
       <c r="N5" t="n">
-        <v>-18009000</v>
+        <v>-44265000</v>
       </c>
       <c r="O5" t="n">
-        <v>-5246000</v>
+        <v>-11622000</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>-15386000</v>
+        <v>-38454000</v>
       </c>
       <c r="S5" t="n">
-        <v>-15386000</v>
+        <v>-38454000</v>
       </c>
       <c r="T5" t="n">
-        <v>-19231000</v>
+        <v>-47629000</v>
       </c>
       <c r="U5" t="n">
-        <v>3845000</v>
+        <v>9175000</v>
       </c>
       <c r="V5" t="n">
-        <v>-16300000</v>
+        <v>-20420000</v>
       </c>
       <c r="W5" t="n">
-        <v>-16300000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-2050000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-2050000</v>
-      </c>
+        <v>-20420000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>-14250000</v>
+        <v>-20420000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1230000</v>
+        <v>3439000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-15480000</v>
+        <v>-23859000</v>
       </c>
       <c r="AC5" t="n">
-        <v>53100000</v>
+        <v>72596000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-582000</v>
+        <v>-492000</v>
       </c>
       <c r="AE5" t="n">
-        <v>102000</v>
+        <v>130000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-11139000</v>
+        <v>-12585000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1005000</v>
+        <v>1214000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-295962000</v>
+        <v>-475794000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-295962000</v>
+        <v>-475794000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>359676000</v>
+        <v>560123000</v>
       </c>
       <c r="AK5" t="n">
-        <v>359676000</v>
+        <v>560123000</v>
       </c>
     </row>
   </sheetData>
@@ -3752,197 +3752,197 @@
       </c>
       <c r="DK1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EX1" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Cameron  Coleman', 'title': 'CEO, MD &amp; Executive Director', 'fiscalYear': 2025, 'totalPay': 611273, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Fergus  Hume', 'title': 'Chief Financial Officer', 'fiscalYear': 2025, 'totalPay': 410042, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Karen  Brown B.Com., L.L.B.', 'title': 'General Counsel &amp; Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John  Stark', 'title': 'Joint Chief Operating Officer of Construction Materials &amp; Services', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Michael  Kemp', 'title': 'Chief Executive Officer of Earth Friendly Concrete', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Cameron  Coleman', 'title': 'CEO, MD &amp; Executive Director', 'fiscalYear': 2025, 'totalPay': 605831, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Fergus  Hume', 'title': 'Chief Financial Officer', 'fiscalYear': 2025, 'totalPay': 406392, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Karen  Brown B.Com., L.L.B.', 'title': 'General Counsel &amp; Company Secretary', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. John  Stark', 'title': 'Joint Chief Operating Officer of Construction Materials &amp; Services', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Michael  Kemp', 'title': 'Chief Executive Officer of Earth Friendly Concrete', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -4053,7 +4053,7 @@
         <v>9</v>
       </c>
       <c r="W2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="X2" t="n">
         <v>1767139200</v>
@@ -4070,34 +4070,34 @@
         <v>4</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.02</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="AL2" t="n">
         <v>1757376000</v>
@@ -4106,31 +4106,31 @@
         <v>0.2013</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="AO2" t="n">
-        <v>27.4</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>15</v>
+        <v>1245</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15</v>
+        <v>1245</v>
       </c>
       <c r="AR2" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.82</v>
+        <v>3.04</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -4139,13 +4139,13 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>547243264</v>
+        <v>579199104</v>
       </c>
       <c r="AZ2" t="n">
-        <v>557669387</v>
+        <v>586717765</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BB2" t="n">
         <v>2.96</v>
@@ -4157,19 +4157,19 @@
         <v>0.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.1959902</v>
+        <v>1.2658292</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.6264</v>
+        <v>2.7068</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.0954</v>
+        <v>2.18665</v>
       </c>
       <c r="BH2" t="n">
         <v>0.032</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.011594203</v>
+        <v>0.011111111</v>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>675409280</v>
+        <v>707365120</v>
       </c>
       <c r="BM2" t="n">
         <v>0.06867000500000001</v>
@@ -4195,16 +4195,16 @@
         <v>0.38921002</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.09814999000000001</v>
+        <v>0.09892999399999999</v>
       </c>
       <c r="BR2" t="n">
         <v>199723828</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.60969335</v>
+        <v>0.6058715</v>
       </c>
       <c r="BT2" t="n">
-        <v>4.4940624</v>
+        <v>4.786494</v>
       </c>
       <c r="BU2" t="n">
         <v>1751241600</v>
@@ -4225,16 +4225,16 @@
         <v>0.1</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.476</v>
+        <v>1.546</v>
       </c>
       <c r="CB2" t="n">
-        <v>9.57</v>
+        <v>10.022</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.5555556</v>
+        <v>1.6666667</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="CE2" t="n">
         <v>0.032</v>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="CH2" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
@@ -4352,143 +4352,143 @@
       </c>
       <c r="DK2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1.6851852</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>1.08 - 2.96</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.059999943</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.02027025</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>166.66667</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1755583200</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1756101600</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1740515400</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1740515400</v>
+      </c>
+      <c r="DX2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.19320011</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.07137584</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.71335006</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.32622963</v>
+      </c>
+      <c r="ED2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1513753200000</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0.01999998</v>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>2.9 - 2.9</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>1782108335</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>finmb_545045623</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="EM2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="EO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>Wagners Holding Company Limited</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>Wagners Holding Company Ltd   R</t>
+        </is>
+      </c>
+      <c r="ER2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ET2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>0.69444376</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="EW2" t="inlineStr">
+        <is>
           <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>1513753200000</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.01999998</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>2.74 - 2.74</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1.6095239</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>1.05 - 2.96</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.22000003</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.07432432999999999</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>155.55556</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1755583200</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1756101600</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1740515400</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1740515400</v>
-      </c>
-      <c r="EB2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.724637</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.113600016</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0.043253127</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.6445999</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.3076262</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EN2" t="n">
-        <v>1780383947</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>finmb_545045623</t>
-        </is>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="ES2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="EU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>Wagners Holding Company Ltd   R</t>
-        </is>
-      </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>Wagners Holding Company Limited</t>
         </is>
       </c>
       <c r="EX2" t="inlineStr"/>
